--- a/Bibsam_tidskriftslistor/scifree_data_bristol.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_bristol.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EEB0C3E-4AD4-408C-AC48-4F219B54D5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9946907B-0ACC-41DA-8A21-CD83D57A18C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1</definedName>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="85">
   <si>
     <t>Imprint</t>
   </si>
@@ -242,6 +243,51 @@
   </si>
   <si>
     <t>https://bristoluniversitypressdigital.com/view/journals/wge/wge-overview.xml</t>
+  </si>
+  <si>
+    <t>2755-6654</t>
+  </si>
+  <si>
+    <t>Feminism and Organization</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypress.co.uk/journals/feminism-and-organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3033-3660 </t>
+  </si>
+  <si>
+    <t>Gender and Justice</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypressdigital.com/view/journals/gj/gj-overview.xml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3050-2969 </t>
+  </si>
+  <si>
+    <t>Journal of Creative Research Methods</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypressdigital.com/view/journals/jcrm/jcrm-overview.xml</t>
+  </si>
+  <si>
+    <t>3049-8414</t>
+  </si>
+  <si>
+    <t>Journal of Disappearance Studies</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypressdigital.com/view/journals/jds/jds-overview.xml</t>
+  </si>
+  <si>
+    <t>2978-2066</t>
+  </si>
+  <si>
+    <t>Pluriversal International Relations</t>
+  </si>
+  <si>
+    <t>https://bristoluniversitypress.co.uk/journals/pluriversal-international-relations</t>
   </si>
 </sst>
 </file>
@@ -441,6 +487,25 @@
     <tableColumn id="7" xr3:uid="{C430790B-0AED-422F-8DC6-ECB5219664ED}" name="CC License options" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{50408A57-0549-43AA-8271-C3EC71348CE8}" name="Table2" displayName="Table2" ref="A1:G26" totalsRowShown="0">
+  <autoFilter ref="A1:G26" xr:uid="{50408A57-0549-43AA-8271-C3EC71348CE8}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G26">
+    <sortCondition ref="D1:D26"/>
+  </sortState>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{BA333AC0-4A50-447C-BC5D-EFBC3A628FA9}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{E975503F-747F-4ABA-914F-5C587C901A19}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{F7720111-A07C-4321-8C3C-5A2196880115}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{AF3ADFE9-3A97-4192-9094-B9AB708C5E16}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{FEFFF09B-3108-46F4-8F7D-AA6B9FFA5309}" name="Journal URL"/>
+    <tableColumn id="6" xr3:uid="{4F55CB05-C0D5-4E34-8D62-B745F3984063}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{96EEA4E8-8308-4B27-9A43-47B74FFCC6E8}" name="CC License options"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1185,7 +1250,567 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05667E0F-E0D2-400C-A261-5A0CEF733736}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="35.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BD97922270BFF5449DC82748B9254CBA" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1a9c31fbfb39900fdbc633c345af06f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="290c3c8b-c505-494e-98a6-958d7e83908a" xmlns:ns3="0d5d58d7-a1b4-432e-9011-e4fc1744b130" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="987c7918b9db7fbf67f42d25d463f8a7" ns2:_="" ns3:_="">
     <xsd:import namespace="290c3c8b-c505-494e-98a6-958d7e83908a"/>
@@ -1376,22 +2001,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05BAD8E2-50EB-4C98-B134-997631A9F2E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="0d5d58d7-a1b4-432e-9011-e4fc1744b130"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="290c3c8b-c505-494e-98a6-958d7e83908a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B718F0FE-2D6E-4288-B4A0-BFB267E86AB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAF2388F-9253-42C7-B53A-9C17716C74B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1408,29 +2043,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B718F0FE-2D6E-4288-B4A0-BFB267E86AB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05BAD8E2-50EB-4C98-B134-997631A9F2E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="0d5d58d7-a1b4-432e-9011-e4fc1744b130"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="290c3c8b-c505-494e-98a6-958d7e83908a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Bibsam_tidskriftslistor/scifree_data_bristol.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_bristol.xlsx
@@ -3,17 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9946907B-0ACC-41DA-8A21-CD83D57A18C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DB29A2-D33C-4E1C-B038-C81858ABEB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1</definedName>
-  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="85">
   <si>
     <t>Imprint</t>
   </si>
@@ -254,18 +250,12 @@
     <t>https://bristoluniversitypress.co.uk/journals/feminism-and-organization</t>
   </si>
   <si>
-    <t xml:space="preserve">3033-3660 </t>
-  </si>
-  <si>
     <t>Gender and Justice</t>
   </si>
   <si>
     <t>https://bristoluniversitypressdigital.com/view/journals/gj/gj-overview.xml</t>
   </si>
   <si>
-    <t xml:space="preserve">3050-2969 </t>
-  </si>
-  <si>
     <t>Journal of Creative Research Methods</t>
   </si>
   <si>
@@ -288,13 +278,19 @@
   </si>
   <si>
     <t>https://bristoluniversitypress.co.uk/journals/pluriversal-international-relations</t>
+  </si>
+  <si>
+    <t>3033-3660</t>
+  </si>
+  <si>
+    <t>3050-2969</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,38 +298,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -341,127 +315,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -475,22 +339,6 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{469435E2-4174-45A6-98CD-BA0886484B4E}" name="Tabell1" displayName="Tabell1" ref="A1:G21" totalsRowShown="0" headerRowDxfId="6">
-  <autoFilter ref="A1:G21" xr:uid="{469435E2-4174-45A6-98CD-BA0886484B4E}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{729245EF-CAEF-488B-BDA7-E92C37CEF549}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{9BDC2C46-4044-484D-BBD9-DE9BD8D06988}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{6C0A4BC6-AA3B-4A83-BBDE-9EAA687920ED}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{177E1537-6912-4165-9521-094A64B2DE54}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{62AB7DF3-141F-41E5-9ACC-7D76DD68EE94}" name="Journal URL"/>
-    <tableColumn id="6" xr3:uid="{580D0C6D-1384-42E0-BD50-6AD73B264D54}" name="Publishing model" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{C430790B-0AED-422F-8DC6-ECB5219664ED}" name="CC License options" dataDxfId="4"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{50408A57-0549-43AA-8271-C3EC71348CE8}" name="Table2" displayName="Table2" ref="A1:G26" totalsRowShown="0">
   <autoFilter ref="A1:G26" xr:uid="{50408A57-0549-43AA-8271-C3EC71348CE8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G26">
@@ -771,486 +619,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="37.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <col min="5" max="5" width="70.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B2:B17">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18 B21">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="E13" r:id="rId1" xr:uid="{D82D53DF-3132-4C17-9E79-3A8B5937E9E3}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{182155EB-E292-47D8-AD48-58AC2D595792}"/>
-    <hyperlink ref="E3" r:id="rId3" xr:uid="{F6AD97D6-2CBE-47C2-BC2E-122DDE7A22BD}"/>
-    <hyperlink ref="E4" r:id="rId4" xr:uid="{DEA71318-5FC6-4907-AE23-8C1AF1FF841A}"/>
-    <hyperlink ref="E5" r:id="rId5" xr:uid="{464F26C4-4497-4E4C-9CE8-1582E8371C99}"/>
-    <hyperlink ref="E6" r:id="rId6" xr:uid="{50FC3D17-58C6-4921-A783-CD4873090908}"/>
-    <hyperlink ref="E7" r:id="rId7" xr:uid="{69F55D46-4D67-445A-AD6D-DC3994D952C6}"/>
-    <hyperlink ref="E8" r:id="rId8" xr:uid="{68C72435-9CF8-4B4F-A0F9-D3AC3FCB4791}"/>
-    <hyperlink ref="E9" r:id="rId9" xr:uid="{EA791384-0906-4BA0-8B3D-03B6EE80BFC5}"/>
-    <hyperlink ref="E10" r:id="rId10" xr:uid="{E5CA514C-1668-45CB-9FAC-EC0AAD705132}"/>
-    <hyperlink ref="E11" r:id="rId11" xr:uid="{270E371C-8C06-4899-8B56-CF3133D29AC5}"/>
-    <hyperlink ref="E12" r:id="rId12" xr:uid="{EB7CAC96-43E0-41D1-BC9B-71B0C3CFD900}"/>
-    <hyperlink ref="E14" r:id="rId13" xr:uid="{9A65071B-0C71-4578-9C4C-64541AAC76F2}"/>
-    <hyperlink ref="E15" r:id="rId14" xr:uid="{E6F2A3B7-F487-4E62-998F-9C9F3C6B440C}"/>
-    <hyperlink ref="E16" r:id="rId15" xr:uid="{561800B3-D9B3-42A3-A497-0CC130E29889}"/>
-    <hyperlink ref="E17" r:id="rId16" xr:uid="{4306F4D5-A0D4-4BEE-8789-7AF9AF2C6AC2}"/>
-    <hyperlink ref="E18" r:id="rId17" xr:uid="{EB4FCC69-AB48-4EC1-93C8-368775A2F330}"/>
-    <hyperlink ref="E19" r:id="rId18" xr:uid="{00C39AC1-CA0E-4ABD-87EA-B612E91260ED}"/>
-    <hyperlink ref="E20" r:id="rId19" xr:uid="{D9A7154C-8F85-4936-9F8D-28F0D6D29990}"/>
-    <hyperlink ref="E21" r:id="rId20" xr:uid="{4A836C9B-C713-4D27-A495-6730308F35B1}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
-  <tableParts count="1">
-    <tablePart r:id="rId22"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05667E0F-E0D2-400C-A261-5A0CEF733736}">
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1452,13 +820,13 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
         <v>73</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>74</v>
-      </c>
-      <c r="E10" t="s">
-        <v>75</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -1532,13 +900,13 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" t="s">
         <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" t="s">
-        <v>78</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1552,13 +920,13 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
         <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" t="s">
-        <v>81</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -1712,13 +1080,13 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
         <v>82</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" t="s">
-        <v>84</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
@@ -1796,21 +1164,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BD97922270BFF5449DC82748B9254CBA" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1a9c31fbfb39900fdbc633c345af06f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="290c3c8b-c505-494e-98a6-958d7e83908a" xmlns:ns3="0d5d58d7-a1b4-432e-9011-e4fc1744b130" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="987c7918b9db7fbf67f42d25d463f8a7" ns2:_="" ns3:_="">
     <xsd:import namespace="290c3c8b-c505-494e-98a6-958d7e83908a"/>
@@ -2001,32 +1354,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05BAD8E2-50EB-4C98-B134-997631A9F2E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="0d5d58d7-a1b4-432e-9011-e4fc1744b130"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="290c3c8b-c505-494e-98a6-958d7e83908a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B718F0FE-2D6E-4288-B4A0-BFB267E86AB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAF2388F-9253-42C7-B53A-9C17716C74B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2043,4 +1386,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B718F0FE-2D6E-4288-B4A0-BFB267E86AB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05BAD8E2-50EB-4C98-B134-997631A9F2E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="0d5d58d7-a1b4-432e-9011-e4fc1744b130"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="290c3c8b-c505-494e-98a6-958d7e83908a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Bibsam_tidskriftslistor/scifree_data_bristol.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_bristol.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DB29A2-D33C-4E1C-B038-C81858ABEB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E850460E-B365-45C1-AD40-21FAF91C00BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
   <si>
     <t>Imprint</t>
   </si>
@@ -241,27 +241,12 @@
     <t>https://bristoluniversitypressdigital.com/view/journals/wge/wge-overview.xml</t>
   </si>
   <si>
-    <t>2755-6654</t>
-  </si>
-  <si>
-    <t>Feminism and Organization</t>
-  </si>
-  <si>
-    <t>https://bristoluniversitypress.co.uk/journals/feminism-and-organization</t>
-  </si>
-  <si>
     <t>Gender and Justice</t>
   </si>
   <si>
     <t>https://bristoluniversitypressdigital.com/view/journals/gj/gj-overview.xml</t>
   </si>
   <si>
-    <t>Journal of Creative Research Methods</t>
-  </si>
-  <si>
-    <t>https://bristoluniversitypressdigital.com/view/journals/jcrm/jcrm-overview.xml</t>
-  </si>
-  <si>
     <t>3049-8414</t>
   </si>
   <si>
@@ -271,19 +256,7 @@
     <t>https://bristoluniversitypressdigital.com/view/journals/jds/jds-overview.xml</t>
   </si>
   <si>
-    <t>2978-2066</t>
-  </si>
-  <si>
-    <t>Pluriversal International Relations</t>
-  </si>
-  <si>
-    <t>https://bristoluniversitypress.co.uk/journals/pluriversal-international-relations</t>
-  </si>
-  <si>
     <t>3033-3660</t>
-  </si>
-  <si>
-    <t>3050-2969</t>
   </si>
 </sst>
 </file>
@@ -339,10 +312,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{50408A57-0549-43AA-8271-C3EC71348CE8}" name="Table2" displayName="Table2" ref="A1:G26" totalsRowShown="0">
-  <autoFilter ref="A1:G26" xr:uid="{50408A57-0549-43AA-8271-C3EC71348CE8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G26">
-    <sortCondition ref="D1:D26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{50408A57-0549-43AA-8271-C3EC71348CE8}" name="Table2" displayName="Table2" ref="A1:G23" totalsRowShown="0">
+  <autoFilter ref="A1:G23" xr:uid="{50408A57-0549-43AA-8271-C3EC71348CE8}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G23">
+    <sortCondition ref="D1:D23"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{BA333AC0-4A50-447C-BC5D-EFBC3A628FA9}" name="Imprint"/>
@@ -620,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05667E0F-E0D2-400C-A261-5A0CEF733736}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -800,13 +773,13 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" t="s">
         <v>70</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>71</v>
-      </c>
-      <c r="E9" t="s">
-        <v>72</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -820,13 +793,13 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -840,13 +813,13 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -860,13 +833,13 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -880,13 +853,13 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -900,13 +873,13 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -920,13 +893,13 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -940,13 +913,13 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
         <v>7</v>
@@ -960,13 +933,13 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
@@ -980,13 +953,13 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
@@ -1000,13 +973,13 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -1020,13 +993,13 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
         <v>7</v>
@@ -1040,13 +1013,13 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -1060,13 +1033,13 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
@@ -1080,78 +1053,18 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
       </c>
       <c r="G23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1355,18 +1268,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1389,14 +1302,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B718F0FE-2D6E-4288-B4A0-BFB267E86AB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05BAD8E2-50EB-4C98-B134-997631A9F2E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -1411,4 +1316,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B718F0FE-2D6E-4288-B4A0-BFB267E86AB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>